--- a/DesignData/Excel_Masters/ArmorAssets_Master.xlsx
+++ b/DesignData/Excel_Masters/ArmorAssets_Master.xlsx
@@ -9,138 +9,167 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21555" windowHeight="8040"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15420" windowHeight="10965"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Rarity" sheetId="3" r:id="rId2"/>
-    <sheet name="Tags" sheetId="2" r:id="rId3"/>
+    <sheet name="ArmorAssets" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t>Item.Type.Armor.Helmet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item.Type.Armor.Chest</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item.Type.Armor.Gloves</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item.Type.Armor.Boots</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Common</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Uncommon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rare</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Epic</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Legendary</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="47">
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>ArmorTag</t>
+  </si>
+  <si>
+    <t>EquipGameplayEffect</t>
+  </si>
+  <si>
+    <t>ItemMesh</t>
+  </si>
+  <si>
+    <t>AttachmentSocket</t>
+  </si>
+  <si>
+    <t>Icon</t>
   </si>
   <si>
     <t>Armor_Displacer</t>
   </si>
   <si>
+    <t>(TagName="Item.Type.Armor.Armor")</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Armor_20011_Displacer.Icon_Armor_20011_Displacer</t>
+  </si>
+  <si>
     <t>Armor_Rescue</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Armor_20021_Rescue.Icon_Armor_20021_Rescue</t>
+  </si>
+  <si>
     <t>Armor_HazmatSuit</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Armor_20031_HazmatSuit.Icon_Armor_20031_HazmatSuit</t>
+  </si>
+  <si>
     <t>Armor_Raiders</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Armor_20041_Raiders.Icon_Armor_20041_Raiders</t>
+  </si>
+  <si>
     <t>Armor_BishopsRobe</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Armor_20051_BishopsRobe.Icon_Armor_20051_BishopsRobe</t>
+  </si>
+  <si>
     <t>Armor_Webrunner</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Armor_20061_Webrunner.Icon_Armor_20061_Webrunner</t>
+  </si>
+  <si>
     <t>Hat_Bluerose</t>
   </si>
   <si>
+    <t>(TagName="Item.Type.Armor.Hat")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Hat_60011_Bluerose.Icon_Hat_60011_Bluerose</t>
+  </si>
+  <si>
     <t>Hat_Angela</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Hat_60021_Angela.Icon_Hat_60021_Angela</t>
+  </si>
+  <si>
     <t>Hat_Tiara</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Hat_60031_Tiara.Icon_Hat_60031_Tiara</t>
+  </si>
+  <si>
     <t>Hat_FeliceHat</t>
   </si>
   <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Hat_60041_FeliceHat.Icon_Hat_60041_FeliceHat</t>
+  </si>
+  <si>
+    <t>(TagName="Item.Type.Armor.Necklace")</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Necklace_50011_ButterflyDance.Icon_Necklace_50011_ButterflyDance</t>
+  </si>
+  <si>
+    <t>Necklace_NecklaceOfGuide</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Necklace_50021_NecklaceOfGuide.Icon_Necklace_50021_NecklaceOfGuide</t>
+  </si>
+  <si>
+    <t>Necklace_NecklaceOfAmplify</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Necklace_50031_NecklaceOfAmplify.Icon_Necklace_50031_NecklaceOfAmplify</t>
+  </si>
+  <si>
+    <t>Necklace_PendantOfPassion</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Necklace_50041_PendantOfPassion.Icon_Necklace_50041_PendantOfPassion</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Ring_30011_RingOfWarrior.Icon_Ring_30011_RingOfWarrior</t>
+  </si>
+  <si>
+    <t>Ring_RingOfAssassin</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Ring_30021_RingOfAssassin.Icon_Ring_30021_RingOfAssassin</t>
+  </si>
+  <si>
+    <t>Ring_RingOfHunter</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Ring_30031_RingOfHunter.Icon_Ring_30031_RingOfHunter</t>
+  </si>
+  <si>
+    <t>Ring_RingOfCommander</t>
+  </si>
+  <si>
+    <t>/Game/External_Assets/UI/Icon/Icon_Equip/Icon_Ring_30041_RingOfCommander.Icon_Ring_30041_RingOfCommander</t>
+  </si>
+  <si>
+    <t>(TagName="Item.Type.Armor.Ring")</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>Necklace_ButterflyDance</t>
-  </si>
-  <si>
-    <t>Necklace_NecklaceOfGuide</t>
-  </si>
-  <si>
-    <t>Necklace_NecklaceOfAmplify</t>
-  </si>
-  <si>
-    <t>Necklace_PendantOfPassion</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>Ring_RingOfWarrior</t>
-  </si>
-  <si>
-    <t>Ring_RingOfAssassin</t>
-  </si>
-  <si>
-    <t>Ring_RingOfHunter</t>
-  </si>
-  <si>
-    <t>Ring_RingOfCommander</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>ItemMesh</t>
-  </si>
-  <si>
-    <t>AttachmentSocket</t>
-  </si>
-  <si>
-    <t>Icon</t>
-  </si>
-  <si>
-    <t>ArmorTag</t>
-  </si>
-  <si>
-    <t>EquipGameplayEffect</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,6 +179,150 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -157,15 +330,188 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -173,21 +519,289 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="강조색1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="강조색2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="강조색3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="강조색4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="강조색5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="강조색6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="경고문" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="계산" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="나쁨" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="메모" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="보통" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="설명 텍스트" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="셀 확인" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="연결된 셀" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="요약" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="입력" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="제목" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="제목 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="제목 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="제목 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="제목 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -468,34 +1082,44 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="19.875" customWidth="1"/>
-    <col min="3" max="3" width="14.5" customWidth="1"/>
-    <col min="4" max="4" width="13.5" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -503,189 +1127,344 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="4">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="중복된 ID (RowName Error)" error="이미 존재하는 ID입니다!_x000a__x000a_RowName(행 이름)은 고유해야 합니다._x000a_(같은 이름을 두 번 쓸 수 없습니다.)_x000a__x000a_다른 이름을 입력해주세요." sqref="A1:A1048576">
-      <formula1>COUNTIF($A:$A, A1) &lt;= 1</formula1>
-    </dataValidation>
-    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="글자 수 초과 (DisplayName)" error="_x000a_아이템 이름이 너무 깁니다! (최대 20자)_x000a__x000a_UI 텍스트 박스를 넘어갈 위험이 있습니다._x000a_더 짧게 줄이거나, 줄바꿈이 필요한지 확인해주세요." sqref="E1">
-      <formula1>20</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="숫자 입력 확인" error="오직 숫자(소수점 가능)만 입력할 수 있습니다." sqref="C20:E1048576 B2:D19">
-      <formula1>-1000000</formula1>
-      <formula2>1000000</formula2>
-    </dataValidation>
-    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="설명 길이 확인" error="설명이 너무 깁니다. (100자 제한)_x000a__x000a_※ 팁:_x000a_줄바꿈이 필요하면 [Alt + Enter]를 사용하세요._x000a_너무 긴 설명은 툴팁 가독성을 해칩니다." sqref="G20:G1048576 F1:F19">
-      <formula1>100</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="선택 오류" error="목록에 없는 값입니다! 드롭다운(▼)을 눌러서 선택해주세요.">
-          <x14:formula1>
-            <xm:f>Tags!$A$25:$A$28</xm:f>
-          </x14:formula1>
-          <xm:sqref>B20:B1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="선택 오류" error="목록에 없는 값입니다! 드롭다운(▼)을 눌러서 선택해주세요.">
-          <x14:formula1>
-            <xm:f>Rarity!$A$1:$A$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>H20:H1048576 G2:G19</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A25:A28"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
